--- a/outputs/relatorio_semanal.xlsx
+++ b/outputs/relatorio_semanal.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Funil" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Por canal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Tendência" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Qualidade dos dados" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Funil" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por canal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tendência" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Qualidade dos dados" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumo'!$A$12:$B$18</definedName>
@@ -459,7 +459,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:38</t>
+          <t>2026-09-28 16:07:04</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:38</t>
+          <t>2026-09-28 16:07:04</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:38</t>
+          <t>2026-09-28 16:07:04</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:38</t>
+          <t>2026-09-28 16:07:04</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28 10:13:38</t>
+          <t>2026-09-28 16:07:04</t>
         </is>
       </c>
     </row>
